--- a/assets/constructions/examples/ctd_mib_disk.xlsx
+++ b/assets/constructions/examples/ctd_mib_disk.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,11 +599,31 @@
           <t>dbc2</t>
         </is>
       </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDC-100-14B-27</t>
+          <t>CDC-160-20B-40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -617,35 +637,35 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="I2" t="n">
+        <v>80</v>
+      </c>
+      <c r="J2" t="n">
         <v>50</v>
       </c>
-      <c r="J2" t="n">
-        <v>40</v>
-      </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -653,23 +673,23 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>SPMT090408</t>
+          <t>SPMT110408</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx027</t>
+          <t>ISO_6462:FDAxx040</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>DER_SP0904H</t>
+          <t>DER_SP1104H</t>
         </is>
       </c>
       <c r="V2" t="n">
@@ -701,35 +721,49 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>SP0904_H</t>
+          <t>SP1104_H</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>544.89</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>44666.76</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12399111600</t>
+          <t>CDC-125-20B-32</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M900</t>
+          <t>CDC</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
         <v>125</v>
@@ -738,22 +772,20 @@
         <v>32</v>
       </c>
       <c r="I3" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="J3" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M3" t="n">
-        <v>6370</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -761,11 +793,11 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>MDHX09T3</t>
+          <t>SPMT110408</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -777,7 +809,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>WIDIA_MDHX09T3H</t>
+          <t>DER_SP1104H</t>
         </is>
       </c>
       <c r="V3" t="n">
@@ -787,7 +819,7 @@
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -796,212 +828,240 @@
         <v>0</v>
       </c>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="n">
-        <v>37</v>
-      </c>
-      <c r="AC3" t="b">
-        <v>1</v>
-      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2017 / WIDIA основной каталог EN</t>
+          <t>2019 / DEREK</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>WID_MDHX09T3_H</t>
+          <t>SP1104_H</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>470.11</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>38536.75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT390K-125B32R10SD08L</t>
+          <t>GDC-80-14B-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MT390K-...R...SD08L</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I4" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="J4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" t="n">
-        <v>11000</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>SDMT08T308EL</t>
+          <t>SNFH1275</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx032</t>
+          <t>ISO_6462:FDAxx022</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SKIF_SD08T3LH</t>
+          <t>DER_SN1275H</t>
         </is>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>SN1275_H</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="n">
         <v>1</v>
       </c>
-      <c r="X4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>309.85</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>25399.61</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GDC-125-14B-32</t>
+          <t>MT390K-100B27R10SD08R</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>СКИФ-М</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MT390K-...R...SD08R</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I5" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="J5" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12500</v>
+      </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>0.7</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>SNFH1275</t>
+          <t>SDMT08T308ER</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx032</t>
+          <t>ISO_6462:FDAxx027</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>DER_SN1275H</t>
+          <t>SKIF_SD08T3RH</t>
         </is>
       </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1010,38 +1070,40 @@
         <v>0</v>
       </c>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>22</v>
+      </c>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
+          <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>SN1275_H</t>
-        </is>
-      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT390K-200C40R14SD08L</t>
+          <t>GDC-160-07B-40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MT390K-...R...SD08L</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1054,83 +1116,99 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="H6" t="n">
         <v>40</v>
       </c>
       <c r="I6" t="n">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="J6" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
-      </c>
-      <c r="M6" t="n">
-        <v>8500</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>SDMT08T308EL</t>
+          <t>SNFH1235</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ISO_6462:SPK02060</t>
+          <t>ISO_6462:FDAxx040</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SKIF_SD08T3LH</t>
+          <t>DER_SN1235H</t>
         </is>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>SN1235_H</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
         <v>1</v>
       </c>
-      <c r="X6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="n">
-        <v>31</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>544.89</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>44666.76</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
